--- a/Курс 2 Сем 1/Алгосы/Lab21/Данные 21 алгосы.xlsx
+++ b/Курс 2 Сем 1/Алгосы/Lab21/Данные 21 алгосы.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\K\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Polytech\Курс 2 Сем 1\Алгосы\Lab21\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D8C1D2-4A17-4184-AB40-7570B788B6BE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3859AE6-EFD0-4473-83DF-F4CC8C57F791}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14388" yWindow="1368" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5760" yWindow="1368" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t>Функция</t>
   </si>
@@ -178,6 +178,15 @@
   </si>
   <si>
     <t xml:space="preserve">Обход в глубину </t>
+  </si>
+  <si>
+    <t>0.000309669 сек</t>
+  </si>
+  <si>
+    <t>0.005505419 сек</t>
+  </si>
+  <si>
+    <t>0.080058399 сек</t>
   </si>
 </sst>
 </file>
@@ -676,6 +685,15 @@
       <c r="A14" t="s">
         <v>47</v>
       </c>
+      <c r="C14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">

--- a/Курс 2 Сем 1/Алгосы/Lab21/Данные 21 алгосы.xlsx
+++ b/Курс 2 Сем 1/Алгосы/Lab21/Данные 21 алгосы.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Polytech\Курс 2 Сем 1\Алгосы\Lab21\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\K\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3859AE6-EFD0-4473-83DF-F4CC8C57F791}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBF93A0D-2022-42B3-B556-80D91206C727}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="1368" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="70">
   <si>
     <t>Функция</t>
   </si>
@@ -165,9 +165,6 @@
     <t>0.000002928 сек</t>
   </si>
   <si>
-    <t>Работа с хеш таблицей (?)</t>
-  </si>
-  <si>
     <t>Пирамидальная сортировка</t>
   </si>
   <si>
@@ -187,6 +184,57 @@
   </si>
   <si>
     <t>0.080058399 сек</t>
+  </si>
+  <si>
+    <t>Хеш таблица</t>
+  </si>
+  <si>
+    <t>Поиск</t>
+  </si>
+  <si>
+    <t>0.000001251 сек</t>
+  </si>
+  <si>
+    <t>0.000003786 сек</t>
+  </si>
+  <si>
+    <t>0.000003635 сек</t>
+  </si>
+  <si>
+    <t>0.000001336 сек</t>
+  </si>
+  <si>
+    <t>0.000001993 сек</t>
+  </si>
+  <si>
+    <t>0.000024324 сек</t>
+  </si>
+  <si>
+    <t>0.000268803 сек</t>
+  </si>
+  <si>
+    <t>0.000040132 сек</t>
+  </si>
+  <si>
+    <t>0.000454548 сек</t>
+  </si>
+  <si>
+    <t>0.000602166 сек</t>
+  </si>
+  <si>
+    <t>0.062099352 сек</t>
+  </si>
+  <si>
+    <t>6.472653470 сек</t>
+  </si>
+  <si>
+    <t>0.000753802 сек</t>
+  </si>
+  <si>
+    <t>0.076900658 сек</t>
+  </si>
+  <si>
+    <t>8.219380830 сек</t>
   </si>
 </sst>
 </file>
@@ -504,7 +552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.109375" bestFit="1" customWidth="1"/>
@@ -678,36 +726,96 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E14" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>54</v>
+      </c>
+      <c r="C15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>50</v>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19" t="s">
+        <v>65</v>
+      </c>
+      <c r="E19" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" t="s">
+        <v>67</v>
+      </c>
+      <c r="D20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/Курс 2 Сем 1/Алгосы/Lab21/Данные 21 алгосы.xlsx
+++ b/Курс 2 Сем 1/Алгосы/Lab21/Данные 21 алгосы.xlsx
@@ -5,27 +5,32 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\K\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\github\Polytech\Курс 2 Сем 1\Алгосы\Lab21\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBF93A0D-2022-42B3-B556-80D91206C727}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{227AE992-041F-43BD-88EA-99F3C75C9400}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="77">
   <si>
     <t>Функция</t>
   </si>
@@ -33,9 +38,6 @@
     <t>BST</t>
   </si>
   <si>
-    <t>Сложность</t>
-  </si>
-  <si>
     <t>100 элементов</t>
   </si>
   <si>
@@ -186,9 +188,6 @@
     <t>0.080058399 сек</t>
   </si>
   <si>
-    <t>Хеш таблица</t>
-  </si>
-  <si>
     <t>Поиск</t>
   </si>
   <si>
@@ -235,13 +234,40 @@
   </si>
   <si>
     <t>8.219380830 сек</t>
+  </si>
+  <si>
+    <t>O(N)</t>
+  </si>
+  <si>
+    <t>O(1)</t>
+  </si>
+  <si>
+    <t>Ожидаемая сложность</t>
+  </si>
+  <si>
+    <t>Фактическая сложность</t>
+  </si>
+  <si>
+    <t>O(logN)</t>
+  </si>
+  <si>
+    <t>O(NlogN)</t>
+  </si>
+  <si>
+    <t>O(N^2)</t>
+  </si>
+  <si>
+    <t>Хеш таблица (Размер 10) - O(N) из-за поиска по массивам в ячейках хеш-таблицы</t>
+  </si>
+  <si>
+    <t>Пирамиды</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -249,13 +275,39 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -267,14 +319,27 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Нейтральный" xfId="2" builtinId="28"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Хороший" xfId="1" builtinId="26"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -552,273 +617,475 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="B5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>11</v>
       </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="B6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="B7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="D7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>13</v>
       </c>
-      <c r="C7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="B9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>15</v>
       </c>
-      <c r="C8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="B10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="D10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>16</v>
       </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="B11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="D11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>17</v>
       </c>
-      <c r="C11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="B12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>43</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>44</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" t="s">
+        <v>57</v>
+      </c>
+      <c r="F14" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" t="s">
+        <v>57</v>
+      </c>
+      <c r="F18" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" t="s">
+        <v>58</v>
+      </c>
+      <c r="E19" t="s">
+        <v>59</v>
+      </c>
+      <c r="F19" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20" t="s">
+        <v>61</v>
+      </c>
+      <c r="F20" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" t="s">
-        <v>58</v>
-      </c>
-      <c r="E14" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15" t="s">
-        <v>60</v>
-      </c>
-      <c r="E15" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" t="s">
-        <v>57</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="B22" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" t="s">
+        <v>50</v>
+      </c>
+      <c r="E22" t="s">
+        <v>51</v>
+      </c>
+      <c r="F22" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" t="s">
+        <v>74</v>
+      </c>
+      <c r="C24" t="s">
         <v>62</v>
       </c>
-      <c r="E16" t="s">
+      <c r="D24" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17" t="s">
-        <v>51</v>
-      </c>
-      <c r="E17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="E24" t="s">
+        <v>64</v>
+      </c>
+      <c r="F24" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>47</v>
-      </c>
-      <c r="C19" t="s">
-        <v>64</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="B25" t="s">
+        <v>74</v>
+      </c>
+      <c r="C25" t="s">
         <v>65</v>
       </c>
-      <c r="E19" t="s">
+      <c r="D25" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>49</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="E25" t="s">
         <v>67</v>
       </c>
-      <c r="D20" t="s">
-        <v>68</v>
-      </c>
-      <c r="E20" t="s">
-        <v>69</v>
+      <c r="F25" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A21:F21"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Курс 2 Сем 1/Алгосы/Lab21/Данные 21 алгосы.xlsx
+++ b/Курс 2 Сем 1/Алгосы/Lab21/Данные 21 алгосы.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\github\Polytech\Курс 2 Сем 1\Алгосы\Lab21\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\K\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{227AE992-041F-43BD-88EA-99F3C75C9400}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C761B00A-DC9F-4E7B-89B9-530B6EF971C6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="77">
   <si>
     <t>Функция</t>
   </si>
@@ -191,33 +191,6 @@
     <t>Поиск</t>
   </si>
   <si>
-    <t>0.000001251 сек</t>
-  </si>
-  <si>
-    <t>0.000003786 сек</t>
-  </si>
-  <si>
-    <t>0.000003635 сек</t>
-  </si>
-  <si>
-    <t>0.000001336 сек</t>
-  </si>
-  <si>
-    <t>0.000001993 сек</t>
-  </si>
-  <si>
-    <t>0.000024324 сек</t>
-  </si>
-  <si>
-    <t>0.000268803 сек</t>
-  </si>
-  <si>
-    <t>0.000040132 сек</t>
-  </si>
-  <si>
-    <t>0.000454548 сек</t>
-  </si>
-  <si>
     <t>0.000602166 сек</t>
   </si>
   <si>
@@ -257,17 +230,44 @@
     <t>O(N^2)</t>
   </si>
   <si>
-    <t>Хеш таблица (Размер 10) - O(N) из-за поиска по массивам в ячейках хеш-таблицы</t>
-  </si>
-  <si>
     <t>Пирамиды</t>
+  </si>
+  <si>
+    <t>0.000002330 сек</t>
+  </si>
+  <si>
+    <t>Хеш таблица</t>
+  </si>
+  <si>
+    <t>0.000001488 сек</t>
+  </si>
+  <si>
+    <t>0.000001252 сек</t>
+  </si>
+  <si>
+    <t>0.000001162 сек</t>
+  </si>
+  <si>
+    <t>0.000001372 сек</t>
+  </si>
+  <si>
+    <t>0.000002476 сек</t>
+  </si>
+  <si>
+    <t>0.000002003 сек</t>
+  </si>
+  <si>
+    <t>0.000001169 сек</t>
+  </si>
+  <si>
+    <t>0.000001326 сек</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -283,16 +283,8 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C5700"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -302,11 +294,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -319,25 +306,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="Нейтральный" xfId="2" builtinId="28"/>
+  <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Хороший" xfId="1" builtinId="26"/>
   </cellStyles>
@@ -617,23 +599,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -645,25 +627,25 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -675,15 +657,15 @@
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
@@ -695,15 +677,15 @@
         <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
         <v>21</v>
@@ -715,15 +697,15 @@
         <v>23</v>
       </c>
       <c r="F5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
         <v>24</v>
@@ -735,15 +717,15 @@
         <v>26</v>
       </c>
       <c r="F6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
         <v>27</v>
@@ -755,15 +737,15 @@
         <v>29</v>
       </c>
       <c r="F7" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C8" t="s">
         <v>30</v>
@@ -775,15 +757,15 @@
         <v>32</v>
       </c>
       <c r="F8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
         <v>33</v>
@@ -795,15 +777,15 @@
         <v>35</v>
       </c>
       <c r="F9" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C10" t="s">
         <v>36</v>
@@ -815,15 +797,15 @@
         <v>38</v>
       </c>
       <c r="F10" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="C11" t="s">
         <v>39</v>
@@ -835,15 +817,15 @@
         <v>41</v>
       </c>
       <c r="F11" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="C12" t="s">
         <v>42</v>
@@ -855,236 +837,165 @@
         <v>44</v>
       </c>
       <c r="F12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="D14" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="E14" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F14" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>52</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="E15" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="F15" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>17</v>
       </c>
       <c r="B16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" t="s">
         <v>69</v>
       </c>
-      <c r="C16" t="s">
+      <c r="E16" t="s">
+        <v>67</v>
+      </c>
+      <c r="F16" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18" t="s">
+        <v>51</v>
+      </c>
+      <c r="F18" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20" t="s">
+        <v>54</v>
+      </c>
+      <c r="E20" t="s">
         <v>55</v>
       </c>
-      <c r="D16" t="s">
-        <v>60</v>
-      </c>
-      <c r="E16" t="s">
-        <v>61</v>
-      </c>
-      <c r="F16" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" t="s">
-        <v>53</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="F20" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" t="s">
         <v>56</v>
       </c>
-      <c r="E18" t="s">
+      <c r="D21" t="s">
         <v>57</v>
       </c>
-      <c r="F18" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19" t="s">
-        <v>69</v>
-      </c>
-      <c r="C19" t="s">
-        <v>54</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="E21" t="s">
         <v>58</v>
       </c>
-      <c r="E19" t="s">
-        <v>59</v>
-      </c>
-      <c r="F19" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20" t="s">
-        <v>60</v>
-      </c>
-      <c r="E20" t="s">
-        <v>61</v>
-      </c>
-      <c r="F20" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>45</v>
-      </c>
-      <c r="B22" t="s">
-        <v>73</v>
-      </c>
-      <c r="C22" t="s">
-        <v>49</v>
-      </c>
-      <c r="D22" t="s">
-        <v>50</v>
-      </c>
-      <c r="E22" t="s">
-        <v>51</v>
-      </c>
-      <c r="F22" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" t="s">
-        <v>74</v>
-      </c>
-      <c r="C24" t="s">
-        <v>62</v>
-      </c>
-      <c r="D24" t="s">
-        <v>63</v>
-      </c>
-      <c r="E24" t="s">
-        <v>64</v>
-      </c>
-      <c r="F24" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>48</v>
-      </c>
-      <c r="B25" t="s">
-        <v>74</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="F21" t="s">
         <v>65</v>
       </c>
-      <c r="D25" t="s">
-        <v>66</v>
-      </c>
-      <c r="E25" t="s">
-        <v>67</v>
-      </c>
-      <c r="F25" t="s">
-        <v>74</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A17:F17"/>
+  <mergeCells count="4">
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A17:F17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
